--- a/Output Files Gemini 3.5 Flash/position_bias/position_bias_summary_gemini.xlsx
+++ b/Output Files Gemini 3.5 Flash/position_bias/position_bias_summary_gemini.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1267,790 +1267,6 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.1077</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.3047</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.2815</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-0.197</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-10.62</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3436</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.4722</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.0206</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5078</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.1286</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-6.24</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.6974</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.7937</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.7872</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.8031</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-0.0963</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-16.14</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.1154</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.3204</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.0201</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.2979</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.3523</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-0.205</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-10.22</v>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>-0.2857</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-0.1162</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.0262</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.1401</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-0.0725</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.1695</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-6.47</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.0857</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.1528</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.0446</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.1286</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.2319</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-0.06710000000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.6657</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.0276</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.6377</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.7101</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-0.06569999999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>-0.2571</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-0.0936</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.0301</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-0.1232</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-0.0435</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-0.1635</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-5.43</v>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>-0.0256</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.3441</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.0346</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.2923</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.3862</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-0.3697</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-10.69</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>5</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.5631</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.0241</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.5385</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.6032</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-0.3323</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-13.78</v>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>5</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.7611</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.0189</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.7385</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.7812</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-0.1611</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-8.539999999999999</v>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>5</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.3352</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.2769</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-0.389</v>
-      </c>
-      <c r="J29" t="n">
-        <v>-10.24</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>5</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0.7111</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.7655</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.7471</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.7816</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-0.0544</v>
-      </c>
-      <c r="J30" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.7667</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.7552</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.0319</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.7069</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.7931</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K31" t="b">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0.9167</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.9828</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.9818</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.9833</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-0.06610000000000001</v>
-      </c>
-      <c r="J32" t="n">
-        <v>-114.48</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.7333</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.0142</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.7845</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="I33" t="n">
-        <v>-0.0667</v>
-      </c>
-      <c r="J33" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>5</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
